--- a/public/StructureDefinition-pghd-pregnancy-status.xlsx
+++ b/public/StructureDefinition-pghd-pregnancy-status.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T16:28:41-06:00</t>
+    <t>2026-09-10T16:32:51-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/public/StructureDefinition-pghd-pregnancy-status.xlsx
+++ b/public/StructureDefinition-pghd-pregnancy-status.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3641" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3641" uniqueCount="571">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-20T16:07:18-05:00</t>
+    <t>2026-10-08T19:53:09-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>Observation.code.coding.system</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/uv/phr/CodeSystem/observation-pghd-codes</t>
   </si>
   <si>
     <t>Observation.code.coding:PGHDCode.version</t>
@@ -6266,7 +6269,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>92</v>
@@ -6300,7 +6303,7 @@
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>311</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6377,10 +6380,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6497,10 +6500,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6540,7 +6543,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>82</v>
@@ -6617,10 +6620,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6737,10 +6740,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6859,13 +6862,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>301</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>82</v>
@@ -6983,7 +6986,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>306</v>
@@ -7101,7 +7104,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>308</v>
@@ -7221,7 +7224,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>310</v>
@@ -7266,7 +7269,7 @@
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>82</v>
@@ -7343,10 +7346,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7463,10 +7466,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7506,7 +7509,7 @@
       </c>
       <c r="Q45" s="2"/>
       <c r="R45" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="S45" t="s" s="2">
         <v>82</v>
@@ -7583,10 +7586,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7703,10 +7706,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7825,10 +7828,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7947,10 +7950,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7973,19 +7976,19 @@
         <v>93</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8034,7 +8037,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8049,19 +8052,19 @@
         <v>104</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8069,10 +8072,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8095,16 +8098,16 @@
         <v>93</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8154,7 +8157,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8178,10 +8181,10 @@
         <v>295</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
@@ -8189,14 +8192,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8215,19 +8218,19 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8276,7 +8279,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8291,19 +8294,19 @@
         <v>104</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8311,14 +8314,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8337,19 +8340,19 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8398,7 +8401,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8413,19 +8416,19 @@
         <v>104</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8433,10 +8436,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8459,16 +8462,16 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8518,7 +8521,7 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8539,13 +8542,13 @@
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8553,10 +8556,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8579,17 +8582,17 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
@@ -8638,7 +8641,7 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8653,19 +8656,19 @@
         <v>104</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
@@ -8673,10 +8676,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8702,16 +8705,16 @@
         <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -8740,7 +8743,7 @@
       </c>
       <c r="Y55" s="2"/>
       <c r="Z55" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8758,7 +8761,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8767,7 +8770,7 @@
         <v>92</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -8776,27 +8779,27 @@
         <v>82</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8911,10 +8914,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9031,10 +9034,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9153,10 +9156,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9271,10 +9274,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9391,10 +9394,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9436,7 +9439,7 @@
       </c>
       <c r="Q61" s="2"/>
       <c r="R61" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S61" t="s" s="2">
         <v>82</v>
@@ -9513,10 +9516,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9633,10 +9636,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9753,10 +9756,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9873,10 +9876,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9995,10 +9998,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10117,10 +10120,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10146,16 +10149,16 @@
         <v>190</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10180,13 +10183,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10204,7 +10207,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10213,7 +10216,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10228,7 +10231,7 @@
         <v>135</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10239,14 +10242,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10268,16 +10271,16 @@
         <v>190</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10302,13 +10305,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10326,7 +10329,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10344,27 +10347,27 @@
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10387,19 +10390,19 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10448,7 +10451,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10469,10 +10472,10 @@
         <v>82</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10483,10 +10486,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10512,13 +10515,13 @@
         <v>190</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10547,10 +10550,10 @@
         <v>290</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>82</v>
@@ -10568,7 +10571,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10586,27 +10589,27 @@
         <v>82</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10632,16 +10635,16 @@
         <v>190</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
@@ -10669,10 +10672,10 @@
         <v>290</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>82</v>
@@ -10690,7 +10693,7 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10711,10 +10714,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10725,10 +10728,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10751,16 +10754,16 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10810,7 +10813,7 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10828,27 +10831,27 @@
         <v>82</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10871,16 +10874,16 @@
         <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10930,7 +10933,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10948,27 +10951,27 @@
         <v>82</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10991,19 +10994,19 @@
         <v>82</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11052,7 +11055,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11064,7 +11067,7 @@
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>82</v>
@@ -11073,10 +11076,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11087,10 +11090,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11205,10 +11208,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11325,14 +11328,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11354,10 +11357,10 @@
         <v>138</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>141</v>
@@ -11412,7 +11415,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11447,10 +11450,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11473,13 +11476,13 @@
         <v>82</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11530,7 +11533,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11539,7 +11542,7 @@
         <v>92</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>104</v>
@@ -11551,10 +11554,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11565,10 +11568,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11591,13 +11594,13 @@
         <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11648,7 +11651,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11657,7 +11660,7 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11669,10 +11672,10 @@
         <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11683,10 +11686,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11712,16 +11715,16 @@
         <v>190</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11749,10 +11752,10 @@
         <v>116</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11770,7 +11773,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11788,13 +11791,13 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11805,10 +11808,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11834,16 +11837,16 @@
         <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
@@ -11871,10 +11874,10 @@
         <v>290</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -11892,7 +11895,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -11910,13 +11913,13 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -11927,10 +11930,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11953,17 +11956,17 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
@@ -12012,7 +12015,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12036,7 +12039,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12047,10 +12050,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12076,10 +12079,10 @@
         <v>205</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12130,7 +12133,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12151,10 +12154,10 @@
         <v>82</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12165,10 +12168,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12191,16 +12194,16 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12250,7 +12253,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12271,10 +12274,10 @@
         <v>82</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12285,10 +12288,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12311,16 +12314,16 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12370,7 +12373,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12391,10 +12394,10 @@
         <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12405,10 +12408,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12431,19 +12434,19 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
@@ -12492,7 +12495,7 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12513,10 +12516,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12527,10 +12530,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12645,10 +12648,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12765,14 +12768,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12794,10 +12797,10 @@
         <v>138</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>141</v>
@@ -12852,7 +12855,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -12887,10 +12890,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12916,13 +12919,13 @@
         <v>190</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>289</v>
@@ -12974,7 +12977,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>92</v>
@@ -12992,7 +12995,7 @@
         <v>82</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>295</v>
@@ -13009,10 +13012,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13035,19 +13038,19 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
@@ -13096,7 +13099,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13114,27 +13117,27 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13160,16 +13163,16 @@
         <v>190</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13194,13 +13197,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13218,7 +13221,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13227,7 +13230,7 @@
         <v>92</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>104</v>
@@ -13242,7 +13245,7 @@
         <v>135</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13253,14 +13256,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13282,16 +13285,16 @@
         <v>190</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13316,13 +13319,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13340,7 +13343,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13358,27 +13361,27 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13404,16 +13407,16 @@
         <v>83</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
@@ -13462,7 +13465,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13483,10 +13486,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
